--- a/ct_scoop_links_2026-05-04.xlsx
+++ b/ct_scoop_links_2026-05-04.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,73 +440,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EAST HARTFORD SCOOP: Demolition begins ahead of large scale development</t>
+          <t>WETHERSFIELD SCOOP: Ortigia Ristorante proposed in Historic Wethersfield!</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-hartford-scoop-demolition-begins-ahead-of-large-scale-development</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/wethersfield-scoop-ortigia-ristorante-proposed-in-historic-wethersfield</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HAMDEN SCOOP: Wonder coming soon to Hamden Plaza!</t>
+          <t>MANCHESTER SCOOP: ConnectiCare building up for lease ahead of closure</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/hamden-scoop-wonder-coming-soon-to-hamden-plaza</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-connecticare-building-up-for-lease-ahead-of-closure</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COLCHESTER SCOOP: Goodwill opening new boutique concept!</t>
+          <t>HARTFORD SCOOP: The Portrait at North Crossing is now leasing!</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/colchester-scoop-goodwill-opening-new-boutique-concept</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/hartford-scoop-the-portrait-at-north-crossing-is-now-leasing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GLASTONBURY SCOOP: The Shops at Somerset Square welcoming 5 new restaurants and a new tenant!</t>
+          <t>NEW HAVEN SCOOP: Papa's Loca sets opening date in New Haven</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/glastonbury-scoop-the-shops-at-somerset-square-welcoming-5-new-restaurants-and-a-new-tenant</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/new-haven-scoop-papas-loca-sets-opening-date-in-new-haven</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>EAST HARTFORD SCOOP: Demolition begins ahead of large scale development</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/east-hartford-scoop-demolition-begins-ahead-of-large-scale-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HAMDEN SCOOP: Wonder coming soon to Hamden Plaza!</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/hamden-scoop-wonder-coming-soon-to-hamden-plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COLCHESTER SCOOP: Goodwill opening new boutique concept!</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/colchester-scoop-goodwill-opening-new-boutique-concept</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GLASTONBURY SCOOP: The Shops at Somerset Square welcoming 5 new restaurants and a new tenant!</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/glastonbury-scoop-the-shops-at-somerset-square-welcoming-5-new-restaurants-and-a-new-tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>SEYMOUR SCOOP: Big Dipper celebrates grand opening in Seymour</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B10" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/seymour-scoop-big-dipper-celebrates-grand-opening-in-seymour</t>
         </is>
